--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO記事AI代行会社" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SEO記事AI代行会社" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -977,6 +977,566 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成代行 安い</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>株式会社PLAN-B</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.plan-b.co.jp/blog/seo/85288/</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成代行会社13選を比較した記事。費用相場や選び方を解説</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成代行 安い</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.geo-code.co.jp/seo/mag/writing-agency/</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作代行サービス会社おすすめ10選を比較した記事</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成代行 安い</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://digitalidentity.co.jp/blog/seo/article-creation-agency.html</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスのおすすめ16社を比較。料金相場・選び方・事例を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成代行 安い</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>株式会社TONOSAMA</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>TONOSAMA（格安SEO記事作成代行）</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>https://seo-taisacu.jp/writing/</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>格安SEO対策会社が提供する記事作成代行サービス。低価格から発注可能</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>4,800円〜（文字数・内容により変動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成代行 安い</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>シュワット株式会社</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行ウルトラ</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://seo-writing-professionals.com/</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>採用率4%の厳選ライター陣による高品質執筆体制。発注本数や契約期間の縛りなし。LLMO対応</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>スタンダードプラン文字単価4円〜、AI記事代行プラン1本16,000円〜、通常プラン文字単価4.5円〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成代行 安い</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>TechSuite株式会社</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://bakuyasu.techsuite.co.jp/30269/</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成代行のおすすめサービス39選を費用と特徴で比較する記事</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO記事 ツール 会社</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>バリュードメイン（GMOグループ）</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Value AI Writer</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.value-domain.com/value-aiwriter/</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>導入文やまとめの文章をSEO最適化して自動生成。チャットワークで完成通知する機能を搭載</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO記事 ツール 会社</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>株式会社Stock Sun</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>https://stock-sun.com/column/seo-ai/</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングの活用方法とおすすめAIツールを紹介する比較記事</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO記事 ツール 会社</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://digi-mado.jp/category/marketing/seo-tools/</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>SEOツール比較記事（全52選中8選をピックアップ）</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO記事 ツール 会社</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>株式会社ウィルゲート</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.willgate.co.jp/promonista/ai-wiriting-tool-recommendation/</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>SEOに強いAIライティングツール10選の比較記事。運営元のウィルゲート自身もTACT SEOというAIライティングツールを提供</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO記事 ツール 会社</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>株式会社シスコム</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gohp.jp/blog/website-operation/5360/</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングツールで60%時短を実現する完全ガイド記事</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO記事 ツール 会社</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>https://n-works.link/blog/seo/seo-article-creation-using-ai-writing</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングを活用したSEO記事作成のポイントを解説する記事</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO記事 ツール 会社</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://oproduct.ai/articles/3887896</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事に使えるAIライティングツールおすすめ比較10選の記事</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO記事 ツール 会社</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>AI-SEO</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://ai-seo.tokyo/lp</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>SEOに強いAIライティングツールのランディングページ</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1537,6 +1537,766 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>株式会社PLAN-B</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.plan-b.co.jp/blog/seo/85288/</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成代行会社13選を比較した記事</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.geo-code.co.jp/seo/mag/writing-agency/</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作代行サービス会社おすすめ10選の比較記事</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>https://takuwil.spool.co.jp/column/article/seo-article-production-agency/</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作代行おすすめ12選（費用相場・選び方・失敗しないポイント）の比較記事</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>https://dream-up.co.jp/marketing/media/seo-article-agency/</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成代行会社おすすめランキング11選の比較記事</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>https://white-link.com/sem-plus/content-writing-agency/</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスおすすめ19選の比較記事</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>株式会社ブリジア</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行Pro</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>納品実績2万本超。キーワード選定から構成・執筆・校正まで完全対応</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>株式会社フルスペック</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツウォーカー</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>累計20万記事以上の作成実績。こだわりコース・プレミアムコースでSEOに配慮した記事制作が可能</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>サクラサクマーケティング</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>1,000人以上のライターネットワークを保有し、報酬単価を高く維持することで品質を担保</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>サイボーグライティング</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>AIとプロ編集者の力を組み合わせた高品質なSEO記事制作サービス</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>1記事9,000円〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 量産 代行 会社</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>ナイル株式会社</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>紙媒体出身のベテラン編集者が企画から品質管理まで一貫対応。制作記事の37.2%がターゲットキーワードで5位以内を獲得</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>株式会社アイティメディア</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.itmedia.co.jp/itselect/ai-writing/article/5300/</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングツール2026年最新比較記事。おすすめ製品10選を紹介</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>https://saas.imitsu.jp/cate-generative-ai</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングツールの選び方・製品一覧比較記事（PRONIアイミツ SaaS）</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>https://saas.imitsu.jp/cate-generative-ai/article/h-2670</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングツール比較。おすすめ3選の無料プランを現役ライターが検証する記事</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>https://boxil.jp/mag/a10168/</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングツールおすすめ比較20選。料金やメリット・選び方ポイントを解説</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>株式会社アイティメディア</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.itmedia.co.jp/itselect/ai-writing/</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング/AI資料作成/AI文章校正のおすすめツール徹底比較記事</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>https://saas.imitsu.jp/cate-generative-ai/serviceList</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングツールのランキング46選。価格や機能、特徴から比較可能</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aspicjapan.org/asu/article/34648</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングツールの比較15選。違いや目的別の選び方を解説</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>https://next-sfa.jp/journal/ai-writing-tool/recommended-ai-writing/</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>おすすめのAIライティングツール比較15選。機能・特長・費用を徹底解説</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>AIライティング SaaS 比較</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>シェアモル株式会社</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Transcope</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>ChatGPT搭載のAIライティングツール。日本語だけでなく英語・中国語でのコンテンツ生成が可能</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2297,6 +2297,646 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 自動生成 サービス</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>リードプラス株式会社</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.leadplus.co.jp/blog/automatically-generate-blog-posts-ai</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>AIでブログ記事を自動生成する方法とおすすめツールを紹介する記事</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 自動生成 サービス</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>AIブログ記事自動生成ツール</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>https://rakkokeyword.com/techo/ai-suggest-article/</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>無料で5000文字以上の記事を自動生成できるツール</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 自動生成 サービス</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>https://note.com/ihayato/n/n313fcd68336a</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>個人が開発した高品質ブログ記事自動生成＆投稿システムの解説記事</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 自動生成 サービス</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>株式会社パンタグラフ</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>https://pantograph.co.jp/blog/production/ai-writting.html</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>記事作成におけるAI活用方法・ツールの種類・出力方法を解説する記事</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 自動生成 サービス</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>NOVEL株式会社</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>SAKUBUN</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>https://sakubun.ai/blog/ai-blog-auto-creation-tool</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事やブログの自動記事作成についておすすめツール6選を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 自動生成 サービス</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Articoolo</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>https://homepage-cube.com/column/ai%E3%81%AB%E3%82%88%E3%82%8B%E8%A8%98%E4%BA%8B%E8%87%AA%E5%8B%95%E4%BD%9C%E6%88%90%E3%82%B5%E3%83%BC%E3%83%93%E3%82%B9%E3%80%8Carticoolo%E3%80%8D%E3%82%92%E8%A9%A6%E3%81%97%E3%81%A6%E3%81%BF%E3%81%9F/</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>AIによる記事自動作成サービスArticooloを試用したレビュー記事</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 自動生成 サービス</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Catchy</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>日本語特化型の文章作成AIサービス。GPT-4系モデル搭載。記事・SNS投稿・広告コピー・メール文など100種類以上のテンプレートに対応</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 自動生成 サービス</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>BuzzTai</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>記事のイメージとキーワードを入力するだけで記事作成が可能。無料版・有料版を提供</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 外注 安い おすすめ</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>株式会社PLAN-B</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.plan-b.co.jp/blog/seo/85288/</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成代行会社13選の比較記事</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 外注 安い おすすめ</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>株式会社Stock Sun</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>https://stock-sun.com/column/seo-articles-request/</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>おすすめのSEO記事制作代行サービスを比較。外注するメリットや選び方も解説する記事</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 外注 安い おすすめ</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>https://kigyolog.com/service.php?id=88</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービス32選の比較記事。コスパの良い外注のコツを紹介</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 外注 安い おすすめ</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>https://btobmarketing-textbook.com/seo-article-cost/</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作の費用相場と外注の選び方を解説する記事</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 外注 安い おすすめ</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>株式会社検索順位の海賊</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>https://search-engine-pirates.co.jp/column/content-seo/seo-article-price/</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成の外注相場（5,000円〜100,000円）と発注本数の目安を解説する記事</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 外注 安い おすすめ</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>シュワット株式会社</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>https://seo-writing-professionals.com/writing-outsourcing/</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>記事外注の依頼先おすすめ26選。費用相場や選び方・格安業者を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 外注 安い おすすめ</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>株式会社エイト</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>市場調査から記事納品までワンストップで依頼可能。コストパフォーマンスが魅力</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>1記事15,000円〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 外注 安い おすすめ</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>株式会社ウィルゲート</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>サグーワークス</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>SEO業界大手ウィルゲートが運営するライティングサービス。安定した品質とスムーズな進行が期待できる</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2937,6 +2937,526 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO対策記事 作成 業者</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>株式会社PLAN-B</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.plan-b.co.jp/blog/seo/85288/</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成代行会社13選の比較記事</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO対策記事 作成 業者</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>株式会社リードエックス</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>AI-SEO記事作成代行</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>https://lead-x.co.jp/seo/ai-seo-writing/</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>ChatGPTなど最新モデルを駆使し、SEOコンサルタントがキーワード選定から検索意図分析まで実施。戦略的な記事構成案を作成</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>20,000円〜（テスト発注可能、業界により変動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO対策記事 作成 業者</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>COUNTER株式会社</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>AI-SEO記事制作/作成代行</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>https://counter-digital.jp/service/ai/</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>検索エンジンのアルゴリズム解析のプロが監修。検索エンジンに評価されるAI記事作成が強み</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>最低5記事/月。具体的な金額は要問い合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO対策記事 作成 業者</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>株式会社リードエックス</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>https://lead-x.co.jp/column/ai-seo-column/</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>AI記事のSEO効果に関するメリット・デメリットと活用法を解説するコラム記事</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO対策記事 作成 業者</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>AI Writer</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>https://ai-writer.jp/</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>国内No.1を謳うSEOライティングツール</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>AI SEO対策記事 作成 業者</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>シュワット株式会社</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行ウルトラ</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>https://seo-writing-professionals.com/</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>AI記事代行プラン（1本16,000円）でコストを抑えつつ、ディレクター編集・SEO最適化付きの高品質記事を量産可能</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>1本16,000円〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 丸投げ 代行</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>https://digitalidentity.co.jp/blog/seo/article-creation-agency.html</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスのおすすめ16社を比較する記事</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 丸投げ 代行</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>https://takuwil.spool.co.jp/column/article/seo-article-production-agency/</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作代行おすすめ12選の比較記事</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 丸投げ 代行</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>株式会社ニュートラルワークス</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作/記事作成代行</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>https://n-works.link/writing</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作・記事作成代行の専門サービスページ</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 丸投げ 代行</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>https://boater.jp/article/1444</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービス比較13選。依頼内容や相場、選び方を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 丸投げ 代行</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>株式会社LiKG（リク）</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成・制作代行</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>https://likg.co.jp/service/article-production/</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成・制作代行の専門サービスページ</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 丸投げ 代行</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>シュワット株式会社</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行ウルトラ</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>https://seo-writing-professionals.com/</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>丸投げ可能なSEO記事制作代行会社</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 丸投げ 代行</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>RankQuest</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>キーワード設計・コンテンツ制作・内部対策・効果測定まで全てワンストップで対応する丸投げ型SEO支援</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3457,6 +3457,486 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツSEO 記事作成 AI 業者</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>バリュードメイン（GMOグループ）</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Value AI Writer</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.value-domain.com/value-aiwriter/</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事生成AIライティングツール。見出し構成や本文をAIが自動生成</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツSEO 記事作成 AI 業者</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>ナイル株式会社</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>記事制作・SEOコンテンツ制作代行サービス</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.seohacks.net/service/content-marketing-production/</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>AIと編集スペシャリストが記事構成から制作までを一貫対応。SEOに強く、収益・ブランディングにつながる成果直結型の記事を制作</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツSEO 記事作成 AI 業者</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>株式会社リードエックス</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>AI-SEO記事作成代行</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>https://lead-x.co.jp/seo/ai-seo-writing/</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>最新の生成AI技術とSEOの専門知識を融合。プロの編集者・ライターが校正・リライトを実施</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>20,000円〜（テスト発注可能、業界により変動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツSEO 記事作成 AI 業者</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>COUNTER株式会社</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>AI-SEO記事制作/作成代行</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>https://counter-digital.jp/service/ai/</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>検索エンジンのアルゴリズム解析のプロが監修する、検索エンジンに評価されるAI記事作成が強み</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>最低5記事/月。具体的な金額は要問い合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツSEO 記事作成 AI 業者</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>https://n-works.link/blog/seo/article-creation-using-generative-ai</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>SEOに強い生成AI活用の記事作成方法とプロンプト例を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツSEO 記事作成 AI 業者</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>TechSuite株式会社</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>バクヤスAI 記事代行</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>https://bakuyasu.techsuite.co.jp/</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>AIが制作・人間が修正するSEO/AIO記事作成代行サービス。AI検索最適化(AIO)対策を総合的に支援</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>15,000円/記事〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成し放題</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>株式会社LANY</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作代行</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lany.co.jp/service/digitalmarketing/writing</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>AI検索最適化(LLMO)×高品質コンテンツ。年間2,000記事の制作実績</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成し放題</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>株式会社PLAN-B</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.plan-b.co.jp/blog/seo/85288/</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成代行会社13選の比較記事</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成し放題</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>株式会社WACUL</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>高品質SEO記事制作代行</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>https://wacul.co.jp/service/seo-content</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>キーワード選定から記事制作、検証、リライトまでエンドツーエンドで支援</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成し放題</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>株式会社PLAN-B</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.plan-b.co.jp/solution/seo/content/</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>高品質な記事を素早く大量に制作でき、他の重要業務に集中できる</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成し放題</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>株式会社検索順位の海賊</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作・ライティング代行</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>https://search-engine-pirates.co.jp/seo-article-production-agency/</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>専門リサーチから記事制作まで一貫して自社で対応し、品質管理基準を徹底</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 作成し放題</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>株式会社LiKG（リク）</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成・制作代行</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>https://likg.co.jp/service/article-production/</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>ライターとディレクターが工程全体の品質管理を担当</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3937,6 +3937,526 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 作成し放題</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>https://japan-ai.co.jp/media/1897/</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成ツールおすすめ比較8選の解説記事</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 作成し放題</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>AI記事（Canva文章生成機能）</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.canva.com/ja_jp/features/ai-kiji/</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>AI文章生成機能で記事を無料作成できるCanvaの機能ページ</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 作成し放題</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>株式会社シンプリック</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>https://simplique.jp/about-generative-ai-tools-for-article-creation/</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成ツール11選の比較記事</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 作成し放題</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>https://fungry.co.jp/cnaps/blog/sentence-generation-ai/</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>AI文章作成ツールおすすめ10選の比較記事</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 作成し放題</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>https://n-works.link/blog/marketing/5-ai-article-creation-tools</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成ツール8選のメリットと注意点を解説する記事</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 作成し放題</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.protea-inc.co.jp/sub-media/ai-article-writing/</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>AIで記事作成する活用方法・注意点・おすすめサービスを解説する記事</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 無制限</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aspicjapan.org/asu/article/41612</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスの比較14選。高品質サービスを選ぶコツを解説する記事</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 無制限</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>https://digitalidentity.co.jp/blog/seo/article-creation-agency.html</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスのおすすめ16社を比較する記事</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 無制限</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>https://kigyolog.com/service.php?id=88</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービス32選の比較記事</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 無制限</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>https://help-you.me/blog/articles_writing/</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービス比較15選。選定ポイントや料金相場を解説する記事</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 無制限</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>https://web-kanji.com/posts/content-service-compare</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスおすすめ16選の比較記事</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 無制限</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行屋</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>https://xn--3kq3hlnz13dlw7bzic.jp/</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>SEO・Webライティングの記事外注サービスのランディングページ</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 無制限</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>シュワット株式会社</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行ウルトラ</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>https://seo-writing-professionals.com/</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>契約期間の縛りなしで利用可能な記事作成代行サービス</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>文字単価2円〜（プランにより変動）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4457,6 +4457,526 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>AI ライティング 無制限</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>https://saas.imitsu.jp/cate-generative-ai/article/l-2416</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>無料プラン・無料トライアルで試せるAIライティングツールおすすめ11選の記事</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>AI ライティング 無制限</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>https://note.com/shushuitie/n/n103038ca53cf</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>副業ライターが実際に使っているAIライティングツール15選の紹介記事</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>AI ライティング 無制限</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>株式会社シンプリック</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>https://simplique.jp/free-ai-writing-tools/</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>無料で使えるAIライティングツール6選の紹介記事</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>AI ライティング 無制限</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>https://n-works.link/blog/seo/free-ai-writing-tool</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>無料で使えるAIライティングツールの選び方・おすすめ13選の記事</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>AI ライティング 無制限</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>https://white-link.com/sem-plus/ai-writing-tools/</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>AIライティングツールおすすめ15選（比較表付き）の記事</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>AI ライティング 無制限</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Jenova AI</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>AIストーリージェネレーター</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jenova.ai/ja/resources/ai-story-generator-free-unlimited-no-restrictions</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>無料・無制限で使えるAIストーリー生成ツール</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>AI ライティング 無制限</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>https://ai-writing.tech/ai-writing/</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>無料のAIライティングツールおすすめ10選を徹底比較する記事</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>AI ライティング 無制限</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>NOVEL株式会社</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>https://n-v-l.co/blog/ai-writing-tool-free</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>無料で使えるAIライティングツールおすすめ12選（完全無料ツールあり）の比較記事</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 何記事でも</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>ナイル株式会社</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.seohacks.net/blog/20719/</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事とは？評価される記事の特徴や作成手順、注意点を解説する記事</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 何記事でも</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>https://n-works.link/blog/seo/seo-rating-points</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事の構成の重要性と作成方法を解説する記事</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 何記事でも</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.conmark.jp/column/seo-contents</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事の検索上位表示を狙う7つのコツと具体例を解説する記事</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 何記事でも</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>https://leadnine.co.jp/media-seo/6417/</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事の書き方19原則、文章構成の作成方法を詳しく解説する記事</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 何記事でも</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>株式会社ブリジア</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行Pro</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>https://article-pro.com/column/foundation/seo-articles/</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事の目的・書き方・記事作成ツール・具体例を徹底解説するコラム記事</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4977,6 +4977,446 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 月額固定 使い放題</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>https://cone-c-slide.com/see-sla/blog/article-price/</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>記事作成の費用相場と費用を左右する要素、依頼のコツを解説する記事</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 月額固定 使い放題</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>株式会社Stock Sun</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>https://stock-sun.com/column/article-production-agency-market-price/</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行の相場（種類・依頼先別）と失敗しない選び方を解説する記事</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 月額固定 使い放題</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>シュワット株式会社</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行ウルトラ</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>https://shwat.jp/ultra/price/</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>AIが高速執筆しSEOディレクターが品質保証する記事作成代行の料金プランページ</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>月額5記事50,000円（税抜）等の定額プランあり</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 月額固定 使い放題</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>定額制コンテンツ記事制作サブスクサービス</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>https://subsc-designoffice.jp/writing/</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>月額制で記事制作を依頼できるサブスクリプション型サービス</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 月額固定 使い放題</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>https://sts-d.com/blog/web-content/content-basics/article-agency-market-price/</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>記事作成の料金相場（ブログ記事・SEO記事・インタビュー記事）を種別ごとに紹介する記事</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 定額 無制限</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lancers.jp/menu/browse/writing_translation/ai_writing</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>AI記事・文章作成が得意なフリーランスに直接依頼する場合の費用相場を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 定額 無制限</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>AI記事（Canva文章生成機能）</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.canva.com/ja_jp/features/ai-kiji/</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>AI文章生成機能で記事を無料作成できるCanvaの機能ページ</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 定額 無制限</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>https://note.com/hiro_seki/n/na7335f0c71ba</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>生成AIサービス12選を料金・機能・活用事例で比較する個人記事</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 定額 無制限</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>https://ai-keiei.shift-ai.co.jp/ai-article-generator-free/</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>無料で使えるAI記事作成ツールおすすめ5選の比較記事（AI経営総合研究所）</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 定額 無制限</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>https://cro-co.co.jp/media/seo/article-creation-ai/</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>記事作成AIおすすめ12選の比較と選び方を解説する記事</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 定額 無制限</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>https://linkeeps.com/ai-services/</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>AI記事制作サービス12選の料金・特徴比較記事</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5417,6 +5417,486 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 サブスク 使い放題</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>株式会社Stock Sun</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>https://stock-sun.com/column/seo-articles-request/</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>おすすめのSEO記事制作代行サービスを比較。外注するメリットや選び方も解説する記事</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 サブスク 使い放題</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.street-academy.com/seo-skill/services/subscription</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>SEOを学べる習い事サブスクリプション・オンラインサロンのまとめページ（学習コンテンツ、記事作成代行ではない）</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 サブスク 使い放題</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>https://web-kanji.com/posts/seo-price</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>SEO対策の費用と相場を徹底解説する記事</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 サブスク 使い放題</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>定額制コンテンツ記事制作サブスクサービス</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>https://subsc-designoffice.jp/writing/</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>月額制で記事制作を依頼できるサブスクリプション型サービス</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 サブスク 使い放題</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>https://withstyle-web.com/column/maintenance/%E3%82%B5%E3%83%96%E3%82%B9%E3%82%AF%E5%9E%8B%E3%83%9B%E3%83%BC%E3%83%A0%E3%83%9A%E3%83%BC%E3%82%B8%E5%88%B6%E4%BD%9C%E3%81%A7seo%E5%AF%BE%E7%AD%96%E3%81%AF%E3%81%A7%E3%81%8D%E3%82%8B%E3%81%AE/</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>サブスク型ホームページ制作サービスにおけるSEO対策の可否を解説する記事</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作 使い放題</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>サイトエンジン株式会社</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.siteengine.co.jp/blog/contents-cost/</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作の代行費用と料金相場、計算方法を徹底解説する記事</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作 使い放題</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lancers.jp/menu/tag/%E3%82%B3%E3%83%B3%E3%83%86%E3%83%B3%E3%83%84%E5%88%B6%E4%BD%9C</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作の依頼・発注・代行ができるクラウドソーシングプラットフォーム</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作 使い放題</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作代行サービス</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>https://cloudcircus.jp/consultinglp/contentcreation/</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作代行のランディングページ</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作 使い放題</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Appmart株式会社（アップマート）</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作代行</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>https://appmart.co.jp/content-marketing/</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作代行の専門サービスページ</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作 使い放題</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>https://takuwil.spool.co.jp/column/article/content-production-company/</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作会社おすすめ12選（費用相場・失敗しないポイント）の記事</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作 使い放題</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>シュワット株式会社</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>https://shwat.jp/ultra/content-production-company/</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作会社おすすめ22選（大手などタイプ別）の比較記事</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作 使い放題</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>シュワット株式会社</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>https://seo-writing-professionals.com/content-production-company/</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>コンテンツ制作会社おすすめ22選（大手などタイプ別）の比較記事（別ドメイン掲載）</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5897,6 +5897,446 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 何本でも 定額</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>https://digitalidentity.co.jp/blog/seo/article-creation-agency.html</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスのおすすめ16社を比較する記事</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 何本でも 定額</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>https://biz.customlife.co.jp/blog/article-creation-costs/</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行の相場をSEO対策や取材など種類別に解説する記事</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 何本でも 定額</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aspicjapan.org/asu/article/41612</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスの比較14選。高品質サービスを選ぶコツを解説する記事</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 何本でも 定額</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>https://kgc-c.co.jp/b-mag/2248</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービス比較10選。料金相場やおすすめの会社を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 何本でも 定額</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>https://boater.jp/article/1444</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービス比較13選。依頼内容や相場、選び方を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 やり放題</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>AI記事（Canva文章生成機能）</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>https://www.canva.com/ja_jp/features/ai-kiji/</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>AI文章生成機能で記事を無料作成できるCanvaの機能ページ</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 やり放題</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>https://ai-keiei.shift-ai.co.jp/ai-article-generator-free/</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>無料で使えるAI記事作成ツールおすすめ5選の比較記事（AI経営総合研究所）</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 やり放題</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>https://n-works.link/blog/marketing/5-ai-article-creation-tools</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成ツール8選のメリットと注意点を解説する記事</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 やり放題</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>https://www.protea-inc.co.jp/sub-media/ai-article-writing/</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>AIで記事作成する活用方法・注意点・おすすめサービスを解説する記事</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 やり放題</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>https://artbrains.co.jp/article/generative-ai/3652/</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>生成AI記事作成おすすめツール10選、SEOへの影響やメリット・デメリットを解説する記事</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 やり放題</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>https://generative-ai.sejuku.net/blog/1051/</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>AI文章作成ツールおすすめ11選（無料・登録なし・媒体別）の記事（侍エンジニア）</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6337,6 +6337,566 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>SEO対策記事 発注し放題</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lancers.jp/menu/tag/SEO%E8%A8%98%E4%BA%8B%E4%BD%9C%E6%88%90</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成の依頼・発注・代行ができるクラウドソーシングプラットフォーム。11〜15記事/月、3,000文字/記事のパッケージ提供あり</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>3,000文字/記事 18,000円〜（パッケージにより変動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>SEO対策記事 発注し放題</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>株式会社PLAN-B</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.plan-b.co.jp/blog/seo/85288/</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成代行会社13選の比較記事</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>SEO対策記事 発注し放題</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>https://hnavi.co.jp/knowledge/blog/seo-cost/</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>SEO外注の費用相場や料金体系を徹底解説する記事（発注ラウンジ）</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>SEO対策記事 発注し放題</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>https://web-kanji.com/posts/seo-price</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>SEO対策の費用と相場を徹底解説する記事</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>SEO対策記事 発注し放題</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>https://coomil.co.jp/column/seowriting-outsourcing/</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>SEOに強い記事の依頼方法、外注先の探し方と費用を解説する記事（デジマーケ）</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>https://rank-quest.jp/column/column/writing-outsourcing/</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスおすすめ6選。外注のポイントや依頼方法を解説する記事（運営：ランクエスト）</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aspicjapan.org/asu/article/41612</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスの比較14選。高品質サービスを選ぶコツを解説する記事</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>https://boxil.jp/mag/a4489/</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>記事制作代行サービスおすすめ比較17選。外注のポイントやメリットを解説する記事</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>https://coconala.com/categories/372</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>記事・Webコンテンツ作成の依頼・外注ができるスキルマーケットプレイス。実績14万件</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>https://fungry.co.jp/cnaps/blog/outsourcing/</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行はSEO戦略設計や効果分析も依頼できることを解説する記事</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>https://web-kanji.com/posts/content-service-compare</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスおすすめ16選の比較記事</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行屋</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>https://xn--3kq3hlnz13dlw7bzic.jp/</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>SEO・Webライティングの記事外注サービスのランディングページ</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>https://boater.jp/article/1444</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービス比較13選。依頼内容や相場、選び方を紹介する記事</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>記事作成 依頼し放題</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>https://white-link.com/sem-plus/content-writing-agency/</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスおすすめ19選の比較記事</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6897,6 +6897,526 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>ライティング 依頼無制限</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>クラウドワークス</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Webライティング外注・代行サービス</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>https://crowdworks.jp/public/employees/skill/496</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>発注手数料無料でWebライティング業務を依頼できるクラウドソーシングサービス</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>ライティング 依頼無制限</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>ランサーズ</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lancers.jp/work/search/writing/writing</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>ライティングの副業・在宅・委託・フリーランスの仕事を探せるクラウドソーシングサイト</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>ライティング 依頼無制限</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>ランサーズ</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lancers.jp/menu/tag/WEB%E3%83%A9%E3%82%A4%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>WEBライティングの依頼・発注・代行ができるクラウドソーシングサイト</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>ライティング 依頼無制限</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Workship ENTERPRISE</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>https://enterprise.goworkship.com/lp/writer/how-to-search</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>アカウント登録料無料、求人掲載無制限、無制限メッセージ機能で候補者と直接交渉できる採用支援プラットフォーム</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>ライティング 依頼無制限</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>株式会社ウィルゲート</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>サグーワークス</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>https://works.sagooo.com/order/</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>SEOコンサルティングやキーワード選定など様々なニーズに対応する記事作成代行サービス</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>ライティング 依頼無制限</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>https://note.com/cannele_writing/n/n0b607441c24b</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>オンライン秘書×ライターの営業手法を解説する個人記事</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>ライティング 依頼無制限</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>ライティング株式会社</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>ゴーストライター代筆サービス</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>https://righting.co.jp/</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>京都で20年以上前から創業した執筆代行会社</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 いくらでも作れる</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>https://biz.customlife.co.jp/blog/article-creation-costs/</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行の相場をSEO対策や取材など種類別に解説する記事</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 いくらでも作れる</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>https://btobmarketing-textbook.com/seo-article-cost/</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事制作の費用相場と外注の選び方を解説する記事</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 いくらでも作れる</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.conmark.jp/column/seo-content-cost</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事の制作費用の目安や内訳、コストダウンのコツを紹介する記事</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 いくらでも作れる</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>株式会社サイダーストーリー</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>https://sider-story.co.jp/knowledge/seo-contents-price/</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事の制作費用相場とコストパフォーマンスを検証する記事</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 いくらでも作れる</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>COUNTER株式会社</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>https://counter-digital.jp/counter-media/article-writing-outsourcing/</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>記事制作の外注先の選び方や適切な費用の見極めポイントを紹介する記事</t>
+        </is>
+      </c>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事 いくらでも作れる</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>株式会社STSデジタル</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>https://sts-d.com/blog/web-content/acquisition/seo-price/</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>SEO記事作成の相場（文字単価・記事単価・月額契約）の費用目安を徹底比較する記事</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7417,6 +7417,526 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 本数制限なし</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>AI記事（Canva文章生成機能）</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>https://www.canva.com/ja_jp/features/ai-kiji/</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>AI文章生成機能で記事を無料作成できるCanvaの機能ページ</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 本数制限なし</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>https://help-you.me/blog/ai-writing/</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成ツール15選、活用方法と注意点を解説する記事</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 本数制限なし</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>https://fungry.co.jp/cnaps/blog/sentence-generation-ai/</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>AI文章作成ツールおすすめ10選の比較記事</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 本数制限なし</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>https://n-works.link/blog/marketing/5-ai-article-creation-tools</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成ツール8選のメリットと注意点を解説する記事</t>
+        </is>
+      </c>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 本数制限なし</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>https://bltz.co.jp/write-text-tool-ai/</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>無料・会員登録なしで使える日本語対応の文章作成AIツールの紹介記事</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 本数制限なし</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>https://generative-ai.sejuku.net/blog/1051/</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>AI文章作成ツールおすすめ11選（無料・登録なし・媒体別）の記事（侍エンジニア）</t>
+        </is>
+      </c>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>AI記事作成 本数制限なし</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>LeapMe</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>https://leap-me.com/ja/app/text-generator</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>無料・登録なしで使えるAI文章作成ツール</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>無料</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 上限なし 月額</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>https://www.onamae.com/business/article/67453/</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスの料金相場、注意点・安く抑える方法を解説する記事（お名前.com）</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 上限なし 月額</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aspicjapan.org/asu/article/41612</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービスの比較14選。高品質サービスを選ぶコツを解説する記事</t>
+        </is>
+      </c>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 上限なし 月額</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>https://biz.customlife.co.jp/blog/article-creation-costs/</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行の相場をSEO対策や取材など種類別に解説する記事</t>
+        </is>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 上限なし 月額</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>株式会社Stock Sun</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>https://stock-sun.com/column/article-production-agency-market-price/</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行の相場（種類・依頼先別）と失敗しない選び方を解説する記事</t>
+        </is>
+      </c>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 上限なし 月額</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>https://subsc-designoffice.jp/blog/contents/comparison-2/</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行サービス比較20選。料金相場と失敗しない選び方を徹底解説する記事</t>
+        </is>
+      </c>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>月額3万円〜10万円前後で一定本数のコンテンツを依頼できるパックプランあり</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行 上限なし 月額</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>オーガニック</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>https://subsc-designoffice.jp/blog/contents/article-writing-fee/</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>記事作成代行の料金相場、外注業者の選び方・文字単価・パック料金を徹底比較する記事</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>取得不可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/SEO記事AI代行会社リスト.xlsx
+++ b/SEO記事AI代行会社リスト.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SEO記事AI代行会社" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO記事AI代行会社" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:I188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -496,6 +497,11 @@
           <t>費用</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>サイト種別</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -536,6 +542,11 @@
           <t>20,000円～（テスト発注可能、業界により変動）</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -576,6 +587,11 @@
           <t>最低5記事/月。具体的な金額は要問い合わせ</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -616,6 +632,11 @@
           <t>1本14,800円～</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -656,6 +677,11 @@
           <t>15,000円/記事～</t>
         </is>
       </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -696,6 +722,11 @@
           <t>1記事4,980円（税別）、月2～100記事対応</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -736,6 +767,11 @@
           <t>1記事18,000～20,000円（発注数により変動）</t>
         </is>
       </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -776,6 +812,11 @@
           <t>月額495円～29,700円（複数プラン展開）</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -816,6 +857,11 @@
           <t>要問い合わせ</t>
         </is>
       </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -856,6 +902,11 @@
           <t>1記事12,000円～</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -896,6 +947,11 @@
           <t>要問い合わせ</t>
         </is>
       </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -936,6 +992,11 @@
           <t>要問い合わせ</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -976,6 +1037,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1016,6 +1082,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1056,6 +1127,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1096,6 +1172,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1136,6 +1217,11 @@
           <t>4,800円〜（文字数・内容により変動）</t>
         </is>
       </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1176,6 +1262,11 @@
           <t>スタンダードプラン文字単価4円〜、AI記事代行プラン1本16,000円〜、通常プラン文字単価4.5円〜</t>
         </is>
       </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1216,6 +1307,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1256,6 +1352,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1296,6 +1397,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1336,6 +1442,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1376,6 +1487,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1416,6 +1532,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1456,6 +1577,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1496,6 +1622,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1536,6 +1667,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1576,6 +1712,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1616,6 +1757,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1656,6 +1802,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1696,6 +1847,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1736,6 +1892,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1776,6 +1937,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1816,6 +1982,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1856,6 +2027,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1896,6 +2072,11 @@
           <t>1記事9,000円〜</t>
         </is>
       </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1936,6 +2117,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1976,6 +2162,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2016,6 +2207,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2056,6 +2252,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2096,6 +2297,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2136,6 +2342,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2176,6 +2387,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2216,6 +2432,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2256,6 +2477,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2296,6 +2522,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2336,6 +2567,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2376,6 +2612,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2416,6 +2657,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2456,6 +2702,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -2496,6 +2747,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2536,6 +2792,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -2576,6 +2837,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2616,6 +2882,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -2656,6 +2927,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -2696,6 +2972,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -2736,6 +3017,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2776,6 +3062,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2816,6 +3107,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2856,6 +3152,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -2896,6 +3197,11 @@
           <t>1記事15,000円〜</t>
         </is>
       </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2936,6 +3242,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -2976,6 +3287,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -3016,6 +3332,11 @@
           <t>20,000円〜（テスト発注可能、業界により変動）</t>
         </is>
       </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3056,6 +3377,11 @@
           <t>最低5記事/月。具体的な金額は要問い合わせ</t>
         </is>
       </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -3096,6 +3422,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -3136,6 +3467,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -3176,6 +3512,11 @@
           <t>1本16,000円〜</t>
         </is>
       </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -3216,6 +3557,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -3256,6 +3602,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -3296,6 +3647,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -3336,6 +3692,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -3376,6 +3737,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -3416,6 +3782,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -3456,6 +3827,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス（URL不明）</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -3496,6 +3872,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -3536,6 +3917,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -3576,6 +3962,11 @@
           <t>20,000円〜（テスト発注可能、業界により変動）</t>
         </is>
       </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -3616,6 +4007,11 @@
           <t>最低5記事/月。具体的な金額は要問い合わせ</t>
         </is>
       </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -3656,6 +4052,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -3696,6 +4097,11 @@
           <t>15,000円/記事〜</t>
         </is>
       </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -3736,6 +4142,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -3776,6 +4187,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -3816,6 +4232,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -3856,6 +4277,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -3896,6 +4322,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -3936,6 +4367,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -3976,6 +4412,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -4016,6 +4457,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -4056,6 +4502,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -4096,6 +4547,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -4136,6 +4592,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -4176,6 +4637,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -4216,6 +4682,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -4256,6 +4727,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -4296,6 +4772,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -4336,6 +4817,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -4376,6 +4862,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -4416,6 +4907,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -4456,6 +4952,11 @@
           <t>文字単価2円〜（プランにより変動）</t>
         </is>
       </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -4496,6 +4997,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -4536,6 +5042,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -4576,6 +5087,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -4616,6 +5132,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -4656,6 +5177,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -4696,6 +5222,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -4736,6 +5267,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -4776,6 +5312,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -4816,6 +5357,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -4856,6 +5402,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -4896,6 +5447,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -4936,6 +5492,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -4976,6 +5537,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -5016,6 +5582,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -5056,6 +5627,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -5096,6 +5672,11 @@
           <t>月額5記事50,000円（税抜）等の定額プランあり</t>
         </is>
       </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -5136,6 +5717,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -5176,6 +5762,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -5216,6 +5807,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -5256,6 +5852,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -5296,6 +5897,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -5336,6 +5942,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -5376,6 +5987,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -5416,6 +6032,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -5456,6 +6077,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -5496,6 +6122,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -5536,6 +6167,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -5576,6 +6212,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -5616,6 +6257,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -5656,6 +6302,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -5696,6 +6347,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -5736,6 +6392,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -5776,6 +6437,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -5816,6 +6482,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -5856,6 +6527,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -5896,6 +6572,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -5936,6 +6617,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -5976,6 +6662,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -6016,6 +6707,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -6056,6 +6752,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -6096,6 +6797,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -6136,6 +6842,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -6176,6 +6887,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -6216,6 +6932,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -6256,6 +6977,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -6296,6 +7022,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -6336,6 +7067,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -6376,6 +7112,11 @@
           <t>3,000文字/記事 18,000円〜（パッケージにより変動）</t>
         </is>
       </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -6416,6 +7157,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -6456,6 +7202,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -6496,6 +7247,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -6536,6 +7292,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -6576,6 +7337,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -6616,6 +7382,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -6656,6 +7427,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -6696,6 +7472,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -6736,6 +7517,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -6776,6 +7562,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -6816,6 +7607,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -6856,6 +7652,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -6896,6 +7697,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -6936,6 +7742,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -6976,6 +7787,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -7016,6 +7832,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -7056,6 +7877,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -7096,6 +7922,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -7136,6 +7967,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -7176,6 +8012,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -7216,6 +8057,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -7256,6 +8102,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -7296,6 +8147,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -7336,6 +8192,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -7376,6 +8237,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -7416,6 +8282,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I175" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -7456,6 +8327,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I176" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -7496,6 +8372,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I177" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -7536,6 +8417,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -7576,6 +8462,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I179" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -7616,6 +8507,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -7656,6 +8552,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -7696,6 +8597,11 @@
           <t>無料</t>
         </is>
       </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>自社サービス公式サイト</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -7736,6 +8642,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -7776,6 +8687,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -7816,6 +8732,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -7856,6 +8777,11 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -7896,6 +8822,11 @@
           <t>月額3万円〜10万円前後で一定本数のコンテンツを依頼できるパックプランあり</t>
         </is>
       </c>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -7936,10 +8867,15 @@
           <t>取得不可</t>
         </is>
       </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>比較・まとめ記事（第三者サイト）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
